--- a/ITech/ProductsDetails.xlsx
+++ b/ITech/ProductsDetails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\GraduationProject\ITech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59D411E-E532-4BE9-A539-9C0DE44432BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AE70CE-95E3-467D-9437-BC8D8A6AFE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="16200" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>ITSIN</t>
   </si>
@@ -64,6 +64,27 @@
   </si>
   <si>
     <t>Graphics Processor: NVIDIA® GeForce® MX330</t>
+  </si>
+  <si>
+    <t>IT-CSV-2</t>
+  </si>
+  <si>
+    <t>title2.1</t>
+  </si>
+  <si>
+    <t>title2.2</t>
+  </si>
+  <si>
+    <t>title2.3</t>
+  </si>
+  <si>
+    <t>content2.1</t>
+  </si>
+  <si>
+    <t>content2.2</t>
+  </si>
+  <si>
+    <t>content2.3</t>
   </si>
 </sst>
 </file>
@@ -391,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -442,7 +463,37 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ITech/ProductsDetails.xlsx
+++ b/ITech/ProductsDetails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\GraduationProject\ITech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AE70CE-95E3-467D-9437-BC8D8A6AFE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370FB01E-0784-4A57-857A-A966DD9E9101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="16200" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>ITSIN</t>
   </si>
@@ -43,48 +43,6 @@
   </si>
   <si>
     <t>Content</t>
-  </si>
-  <si>
-    <t>IT-CSV-1</t>
-  </si>
-  <si>
-    <t>Momory</t>
-  </si>
-  <si>
-    <t>Installed Memory: 8 GB RAM</t>
-  </si>
-  <si>
-    <t>Processor</t>
-  </si>
-  <si>
-    <t>Intel® Core™ i7-10510U Processor, 1.80 GHz (8M Cache, up to 4.9 GHz, # of Cores: 4)</t>
-  </si>
-  <si>
-    <t>Graphics</t>
-  </si>
-  <si>
-    <t>Graphics Processor: NVIDIA® GeForce® MX330</t>
-  </si>
-  <si>
-    <t>IT-CSV-2</t>
-  </si>
-  <si>
-    <t>title2.1</t>
-  </si>
-  <si>
-    <t>title2.2</t>
-  </si>
-  <si>
-    <t>title2.3</t>
-  </si>
-  <si>
-    <t>content2.1</t>
-  </si>
-  <si>
-    <t>content2.2</t>
-  </si>
-  <si>
-    <t>content2.3</t>
   </si>
 </sst>
 </file>
@@ -429,71 +387,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A6" s="2"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
+      <c r="A7" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ITech/ProductsDetails.xlsx
+++ b/ITech/ProductsDetails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\GraduationProject\ITech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370FB01E-0784-4A57-857A-A966DD9E9101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5A40FD-3491-41AD-A09D-BF4AC60AB5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>ITSIN</t>
   </si>
@@ -43,6 +43,51 @@
   </si>
   <si>
     <t>Content</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>IT-CSV-1</t>
+  </si>
+  <si>
+    <t>GSM / HSPA / LTE</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <r>
+      <t>Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: LCD, 90Hz</t>
+    </r>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <r>
+      <t>OS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Android 11, MIUI 12.5</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -387,6 +432,39 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>

--- a/ITech/ProductsDetails.xlsx
+++ b/ITech/ProductsDetails.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\workspace\GraduationProject\ITech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohamed\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5A40FD-3491-41AD-A09D-BF4AC60AB5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD2E213E-B62A-4886-8412-7B80BDE99EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,9 +23,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="283">
   <si>
     <t>ITSIN</t>
   </si>
@@ -57,22 +55,732 @@
     <t>Display</t>
   </si>
   <si>
-    <r>
-      <t>Type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: LCD, 90Hz</t>
-    </r>
-  </si>
-  <si>
     <t>Platform</t>
+  </si>
+  <si>
+    <t>HSPA 21.1/5.76 Mbps, LTE Cat4 150/50 Mbps</t>
+  </si>
+  <si>
+    <t>6.6 inches, 105.2 cm2 (~83.2% screen-to-Body ratio)</t>
+  </si>
+  <si>
+    <t> Android 10 (Go edition)</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>165.4 x 76.4 x 8.8 mm</t>
+  </si>
+  <si>
+    <t>Memory</t>
+  </si>
+  <si>
+    <t>microSDXC (dedicated slot)</t>
+  </si>
+  <si>
+    <t>Main Camera</t>
+  </si>
+  <si>
+    <t>8 MP + QVGA</t>
+  </si>
+  <si>
+    <t>Selfie Camera</t>
+  </si>
+  <si>
+    <t>Dual-LED flash</t>
+  </si>
+  <si>
+    <t>Communications</t>
+  </si>
+  <si>
+    <t>Wi-Fi 802.11 a/b/g/n/ac, dual-band, Wi-Fi Direct, hotspot</t>
+  </si>
+  <si>
+    <t>Features</t>
+  </si>
+  <si>
+    <t>Fingerprint (rear-mounted), accelerometer, gyro, proximity</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t> Li-Po 5000 mAh, non-removable</t>
+  </si>
+  <si>
+    <t>IT-CSV-2</t>
+  </si>
+  <si>
+    <t>Android 11 realme UI</t>
+  </si>
+  <si>
+    <t>IPS LCD</t>
+  </si>
+  <si>
+    <t>165.2 × 76.4 × 8.9 mm</t>
+  </si>
+  <si>
+    <t>16 MP + QVGA</t>
+  </si>
+  <si>
+    <t>Wi-Fi 751.11 a/b/g/n/ac, dual-band, Wi-Fi Direct, hotspot</t>
+  </si>
+  <si>
+    <t>IT-CSV-3</t>
+  </si>
+  <si>
+    <t>HSDPA 850 / 900 / 2100</t>
+  </si>
+  <si>
+    <t>720 x 1600 pixels, 20:9 ratio (~264 ppi density)</t>
+  </si>
+  <si>
+    <t>Android 10</t>
+  </si>
+  <si>
+    <t>164 x 75.8 x 8.9 mm</t>
+  </si>
+  <si>
+    <t> 48 MP, f/2.0, 26mm (wide), AF</t>
+  </si>
+  <si>
+    <t>8 MP, f/2.2</t>
+  </si>
+  <si>
+    <t> Wi-Fi 802.11 b/g/n, Wi-Fi Direct, hotspot</t>
+  </si>
+  <si>
+    <t>Li-Po 5000 mAh, non-removable</t>
+  </si>
+  <si>
+    <t>IT-CSV-4</t>
+  </si>
+  <si>
+    <t>GSM 850 / 900 / 1800 / 1900 - SIM 1 &amp; SIM 2</t>
+  </si>
+  <si>
+    <t>6.5 inches, 102.0 cm2 (~83.4% screen-to-body ratio)</t>
+  </si>
+  <si>
+    <t>Android 11, MIUI 12.5</t>
+  </si>
+  <si>
+    <t>162 x 75.5 x 8.9 mm</t>
+  </si>
+  <si>
+    <t>128GB 4GB RAM</t>
+  </si>
+  <si>
+    <t>50 MP, f/1.8, (wide), PDAF</t>
+  </si>
+  <si>
+    <t>8 MP, f/2.0, (wide)</t>
+  </si>
+  <si>
+    <t>IT-CSV-5</t>
+  </si>
+  <si>
+    <t>GSM 850 / 900 / 1800 / 1900</t>
+  </si>
+  <si>
+    <t>6.5 inches, 106.7 cm2 (~85.8% screen-to-Body ratio)</t>
+  </si>
+  <si>
+    <t>48 MP, f/2.0, 26mm (wide), AF</t>
+  </si>
+  <si>
+    <t>Wi-Fi 802.11 b/g/n, Wi-Fi Direct, hotspot</t>
+  </si>
+  <si>
+    <t>IT-CSV-6</t>
+  </si>
+  <si>
+    <t>HSDPA 850 / 900 / 1900 / 2100</t>
+  </si>
+  <si>
+    <t>IT-CSV-7</t>
+  </si>
+  <si>
+    <t>IPS LCD capacitive touchscreen, 16M colors</t>
+  </si>
+  <si>
+    <t>Android 9.0 (Pie)</t>
+  </si>
+  <si>
+    <t>164.9 x 75.8 x 8.4 mm</t>
+  </si>
+  <si>
+    <t>128GB ROM, 6GB RAM</t>
+  </si>
+  <si>
+    <t>16 MP, f/1.8, 27mm (wide), 1/2.8", 1.12µm, PDAF</t>
+  </si>
+  <si>
+    <t>8 MP, f/2.0, 25mm (wide), 1/4", 1.12µm</t>
+  </si>
+  <si>
+    <t> Fingerprint (rear-mounted), accelerometer, proximity</t>
+  </si>
+  <si>
+    <t>Battery charging 10W</t>
+  </si>
+  <si>
+    <t>IT-CSV-8</t>
+  </si>
+  <si>
+    <t>IT-CSV-9</t>
+  </si>
+  <si>
+    <t>HSPA 42.2/5.76 Mbps, LTE-A</t>
+  </si>
+  <si>
+    <t>6.43 inches, 99.8 cm2 (~83.5% screen-to-body ratio)</t>
+  </si>
+  <si>
+    <t>160.5 x 74.5 x 8.3 mm</t>
+  </si>
+  <si>
+    <t>128GB 8GB RAM</t>
+  </si>
+  <si>
+    <t>64 MP, f/1.8, 26mm (wide), 1/1.97", 0.7µm, PDAF</t>
+  </si>
+  <si>
+    <t>13 MP, f/2.5, (wide), 1/3.06", 1.12µm</t>
+  </si>
+  <si>
+    <t>Li-Po 5000 mAh, non-removabl</t>
+  </si>
+  <si>
+    <t>IT-CSV-10</t>
+  </si>
+  <si>
+    <t>IT-CSV-11</t>
+  </si>
+  <si>
+    <t>HSPA 42.2/5.76 Mbps, LTE-A (CA) Cat18 1200/150 Mbps, 5G</t>
+  </si>
+  <si>
+    <t>6.5 inches, 102.0 cm2 (~84.9% screen-to-body ratio)</t>
+  </si>
+  <si>
+    <t>Android 11, One UI 3.1</t>
+  </si>
+  <si>
+    <t>159.9 x 75.1 x 8.4 mm</t>
+  </si>
+  <si>
+    <t>128GB, 8GB RAM</t>
+  </si>
+  <si>
+    <t>64 MP, f/1.8, 26mm (wide), 1/1.7", 0.8µm, PDAF, OIS</t>
+  </si>
+  <si>
+    <t> 32 MP, f/2.2, 26mm (wide), 1/2.8", 0.8µm</t>
+  </si>
+  <si>
+    <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, Wi-Fi Direct, hotspot</t>
+  </si>
+  <si>
+    <t>IT-CSV-12</t>
+  </si>
+  <si>
+    <t>163.8 x 75.6 x 8.4 mm</t>
+  </si>
+  <si>
+    <t>OS Android 11</t>
+  </si>
+  <si>
+    <t>163.8 x 75.6 x 8.4 mm (6.45 x 2.98 x 0.33 in)</t>
+  </si>
+  <si>
+    <t>Card slot microSDXC</t>
+  </si>
+  <si>
+    <t>13 MP, f/2.2, 26mm (wide), 1/3.06", 1.12µm, PDAF</t>
+  </si>
+  <si>
+    <t>Single 8 MP, f/2.0, (wide)</t>
+  </si>
+  <si>
+    <t>IT-CSV-13</t>
+  </si>
+  <si>
+    <t>IT-CSV-14</t>
+  </si>
+  <si>
+    <t>HSDPA 850 / 900 / 1700(AWS) / 1900 / 2100</t>
+  </si>
+  <si>
+    <t>1284 x 2778 pixels, 19.5:9 ratio (~458 ppi density)</t>
+  </si>
+  <si>
+    <t>iOS 15</t>
+  </si>
+  <si>
+    <t>160.8 x 78.1 x 7.7 mm</t>
+  </si>
+  <si>
+    <t>256GB 6GB RAM</t>
+  </si>
+  <si>
+    <t>12 MP, f/1.5, 26mm (wide), 1.9µm, dual pixel PDAF, sensor-shift OIS</t>
+  </si>
+  <si>
+    <t>12 MP, f/2.2, 23mm (wide), 1/3.6</t>
+  </si>
+  <si>
+    <t>Wi-Fi 802.11 a/b/g/n/ac/6, dual-band, hotspot</t>
+  </si>
+  <si>
+    <t>Li-Ion 4373 mAh, non-removable (16.75 Wh</t>
+  </si>
+  <si>
+    <t>IT-CSV-15</t>
+  </si>
+  <si>
+    <t>IT-CSV-16</t>
+  </si>
+  <si>
+    <t>IT-CSV-17</t>
+  </si>
+  <si>
+    <t>IT-CSV-18</t>
+  </si>
+  <si>
+    <t>GSM 850/900/1800/1900</t>
+  </si>
+  <si>
+    <t>COMMS WLAN Wi-Fi 802.11 a / b / g / n / ac</t>
+  </si>
+  <si>
+    <t>132GB 6GB RAM</t>
+  </si>
+  <si>
+    <t>IT-CSV-19</t>
+  </si>
+  <si>
+    <t>IT-CSV-20</t>
+  </si>
+  <si>
+    <t>Processor</t>
+  </si>
+  <si>
+    <t>Intel® Core™ i3-1005G1 Processor 1.20 GHz (4M Smart Cache, up to 3.40 GHz, # of Cores: 2)</t>
+  </si>
+  <si>
+    <t>4 GB DDR4-2666 MHz RAM (1 x 4 GB)</t>
+  </si>
+  <si>
+    <t>15.6" diagonal, HD (1366 x 768), narrow bezel, anti-glare, 250 nits, 45% NTSC</t>
+  </si>
+  <si>
+    <t>Graphics</t>
+  </si>
+  <si>
+    <t>Intel® UHD Graphics</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Internal drive: 1 TB 5400 rpm SATA HDD</t>
+  </si>
+  <si>
+    <t>I/O Ports</t>
+  </si>
+  <si>
+    <t>2 Super Speed USB Type-A 5Gbps signaling rate</t>
+  </si>
+  <si>
+    <t>Expansion slots</t>
+  </si>
+  <si>
+    <t>1 multi-format digital media reader</t>
+  </si>
+  <si>
+    <t>Hardware</t>
+  </si>
+  <si>
+    <t>Audio: Stereo speakers, integrated digital microphone</t>
+  </si>
+  <si>
+    <t>IT-CSV-21</t>
+  </si>
+  <si>
+    <t> Intel Core i3-1005G1 (2C / 4T, 1.2 / 3.4GHz, 4MB)</t>
+  </si>
+  <si>
+    <t>4GB Soldered DDR4-2666</t>
+  </si>
+  <si>
+    <t> Integrated Intel UHD Graphics</t>
+  </si>
+  <si>
+    <t>15.6" FHD (1920x1080) TN 220nits Anti-glare</t>
+  </si>
+  <si>
+    <t>1TB HDD 5400rpm 2.5</t>
+  </si>
+  <si>
+    <t>FreeDOS</t>
+  </si>
+  <si>
+    <t>Card Reader</t>
+  </si>
+  <si>
+    <t>4-in-1 Card Reader</t>
+  </si>
+  <si>
+    <t>WLAN + Bluetooth</t>
+  </si>
+  <si>
+    <t>11ac, 1x1 + BT4.2</t>
+  </si>
+  <si>
+    <t>IT-CSV-22</t>
+  </si>
+  <si>
+    <t>11th Generation Intel® Core™ i5-1135G7 Processor (8MB Cache, 2.40 GHz up to 4.2 GHz),4 cores , 8 threads</t>
+  </si>
+  <si>
+    <t>8GB DDR4, 3200MHz</t>
+  </si>
+  <si>
+    <t>15.6-inch HD (1366 x 768) Anti-glare LED Backlight Non-Touch Narrow Border WVA Display</t>
+  </si>
+  <si>
+    <t> NVIDIA® GeForce® MX330 with 2GB GDDR5 graphics memory</t>
+  </si>
+  <si>
+    <t>1TB 5400 rpm Hard Drive</t>
+  </si>
+  <si>
+    <t> 3-in-1 SD Media Card</t>
+  </si>
+  <si>
+    <t>USB 3.2 Gen 1 Type-C™ (Data only)</t>
+  </si>
+  <si>
+    <t> 802.11ac 1x1 WiFi and Bluetooth</t>
+  </si>
+  <si>
+    <t>IT-CSV-23</t>
+  </si>
+  <si>
+    <t>IT-CSV-24</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 3 3300U Mobile Processor, 2.10 GHz</t>
+  </si>
+  <si>
+    <t>4GBMemory Type: DDR4 2400MHz</t>
+  </si>
+  <si>
+    <t>Screen Size: 14-inchResolution: HD (1366 x 768)</t>
+  </si>
+  <si>
+    <t>Graphics Processor: Integrated AMD Radeon Vega 6 GraphicsGraphics Video RAM: Shared</t>
+  </si>
+  <si>
+    <t>1TBStorage Technology: 5400rpm</t>
+  </si>
+  <si>
+    <t>2 USB 3.1 Gen 1</t>
+  </si>
+  <si>
+    <t> AC power1 multi-format digital media reader</t>
+  </si>
+  <si>
+    <t>Wi-Fi 802.11 acBluetooth® 4.2</t>
+  </si>
+  <si>
+    <t>IT-CSV-25</t>
+  </si>
+  <si>
+    <t>IT-CSV-26</t>
+  </si>
+  <si>
+    <t>IT-CSV-27</t>
+  </si>
+  <si>
+    <t>Intel® Core™ i3-10110U Processor, 2.10 GHz (4M Cache, Max Turbo Frequency up to 4.10 GHz, # of Cores: 2)</t>
+  </si>
+  <si>
+    <t>Installed Memory: 4 GB RAM</t>
+  </si>
+  <si>
+    <t>Screen Size: 15.6-inch</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce MX130 2GB GDDR5</t>
+  </si>
+  <si>
+    <t>Storage Capacity: 1TB SATA HDD</t>
+  </si>
+  <si>
+    <t>2 x USB-A 3.1 Gen 1</t>
+  </si>
+  <si>
+    <t>Camera: 0.3MP Fixed Focus camera with Dual Microphone</t>
+  </si>
+  <si>
+    <t>Wi-Fi 802.11 b/g/n/ac 2x2</t>
+  </si>
+  <si>
+    <t>IT-CSV-28</t>
+  </si>
+  <si>
+    <t>IT-CSV-29</t>
+  </si>
+  <si>
+    <t>IT-CSV-30</t>
+  </si>
+  <si>
+    <t>Intel® Core ™ i3-1115G4 3.0</t>
+  </si>
+  <si>
+    <t>3 USB 3.1 Gen 1</t>
+  </si>
+  <si>
+    <t>IT-CSV-31</t>
+  </si>
+  <si>
+    <t> 11th Gen Intel Core i7 - 11370H - Speed: 3.3 GHz (Base) - 4.8 GHz (Max) - 4 Cores - 8 Threads - 12MB Cache</t>
+  </si>
+  <si>
+    <t>Cooling</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>Wireless</t>
+  </si>
+  <si>
+    <t>8GB RAM DDR4-3200</t>
+  </si>
+  <si>
+    <t>256GB SSD + 1TB hdd</t>
+  </si>
+  <si>
+    <t>15.6" FHD (1920x1080) - IPS Technology - 120 Hz Refresh Rate - 250Nits Brightness</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3050 4GB GDDR6 Dedicated Graphics with max TGP 90W - Boost Clock 1500/1740MHz</t>
+  </si>
+  <si>
+    <t>100%imporved ventilation rate - 21% larger thermal Area - 35% higher TDP</t>
+  </si>
+  <si>
+    <t>Pre-Loaded Windows 10 Home with Lifetime Validity</t>
+  </si>
+  <si>
+    <t>IT-CSV-32</t>
+  </si>
+  <si>
+    <t>IT-CSV-33</t>
+  </si>
+  <si>
+    <t>IT-CSV-34</t>
+  </si>
+  <si>
+    <t>IT-CSV-35</t>
+  </si>
+  <si>
+    <t>Intel® Core™ i5-1035G1 (1.0 GHz base frequency, up to 3.6 GHz with Intel® Turbo Boost Technology, 6 MB L3 cache, 4 cores)</t>
+  </si>
+  <si>
+    <t>8 GB DDR4-2666 SDRAM (1 x 8 GB)</t>
+  </si>
+  <si>
+    <t>1 TB 5400 rpm SATA HDD</t>
+  </si>
+  <si>
+    <t>39.6 cm (15.6") diagonal, HD (1366 x 768), anti-glare, 220 nits, 45% NTSC</t>
+  </si>
+  <si>
+    <t>Integrated: Intel UHD Graphics</t>
+  </si>
+  <si>
+    <t>Memory </t>
+  </si>
+  <si>
+    <t>Storage </t>
+  </si>
+  <si>
+    <t>Intel® Core™ i7-1065G7 (1.3 GHz base frequency, up to 3.9 GHz with Intel® Turbo Boost Technology, 8 MB L3 cache, 4 cores)</t>
+  </si>
+  <si>
+    <t>Intel® Iris® Plus Graphics</t>
+  </si>
+  <si>
+    <t>Operating System: Windows 10 Home 64, English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrated 10/100/1000 GbE NIC Realtek RTL8821CE 802.11a/b/g/n/ac (1x1) Wi-Fi® Bluetooth® 4.2
+</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>Intel® Core™ i3-1115G4 (up to 4.1 GHz with Intel® Turbo Boost Technology, 6 MB L3 cache, 2 cores</t>
+  </si>
+  <si>
+    <t>39.6 cm (15.6") diagonal, HD (1366 x 768), micro-edge, anti-glare, 250 nits, 45% NTSC</t>
+  </si>
+  <si>
+    <t>Realtek RTL8821CE-M 802.11a/b/g/n/ac (1x1) Wi-Fi® and Bluetooth® 4.2 combo</t>
+  </si>
+  <si>
+    <t>Windows 10 Home 64</t>
+  </si>
+  <si>
+    <t>Intel® Core™ i7-1065G7 (1.3 GHz base frequency, up to 3.9 GHz base with Intel® Turbo Boost Technology, 8 MB cache, 4 cores)</t>
+  </si>
+  <si>
+    <t>16 GB DDR4 SDRAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal drive: 512SSD Optical drive: None
+</t>
+  </si>
+  <si>
+    <t>15.6” Full HD (1920 x 1080) TN, anti-glare</t>
+  </si>
+  <si>
+    <t>Intel Iris Plus graphics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wi-Fi: Intel® Dual Band Wireless-AC 802.11ac  WiFi Bluetooth® 5.0
+</t>
+  </si>
+  <si>
+    <t>Operating System: DOS</t>
+  </si>
+  <si>
+    <t>IT-CSV-36</t>
+  </si>
+  <si>
+    <t>11th Generation Intel® Core™ i7-1165G7 Processor (12MB Cache, 2.80 GHz up to 4.7 GHz),4 cores , 8 threads</t>
+  </si>
+  <si>
+    <t> 8GB DDR4, 3200MHz</t>
+  </si>
+  <si>
+    <t>512 SSD Hard Drive</t>
+  </si>
+  <si>
+    <t>15.6-inch FHD (1920 x 1080) Anti-glare LED Backlight Non-Touch Narrow Border WVA Display</t>
+  </si>
+  <si>
+    <t> 802.11ac 1x1 WiFi and Bluetooth 5.0</t>
+  </si>
+  <si>
+    <t>IT-CSV-37</t>
+  </si>
+  <si>
+    <t> Intel® Celeron® N4020 (1.1 GHz base frequency, up to 2.8 GHz burst frequency, 4 MB cache, 2 cores)</t>
+  </si>
+  <si>
+    <t>4 GB DDR4-2400 SDRAM (1 x 4 GB)</t>
+  </si>
+  <si>
+    <t>64 GB eMMC</t>
+  </si>
+  <si>
+    <t>14" diagonal, HD (1366 x 768), micro-edge, BrightView, 220 nits, 45% NTSC</t>
+  </si>
+  <si>
+    <t>802.11ac (1x1) Wi-Fi® and Bluetooth® 4.2 combo</t>
+  </si>
+  <si>
+    <t>Windows 10 Home in S mode</t>
+  </si>
+  <si>
+    <t>IT-CSV-38</t>
+  </si>
+  <si>
+    <t>Intel® Core™ i5-10210U Processor, 1.60 GHz (6M Cache, up to 3.9 GHz, # of Cores: 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installed Memory: 8 GB RAM Memory Type: DDR4-2666
+</t>
+  </si>
+  <si>
+    <t>Storage Capacity: 1TB HDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen Size: 15.6-inch  Resolution: FHD (1920 x 1080)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graphics Processor: NVIDIA® GeForce® MX130 Graphics Video RAM: 2GB GDDR5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethernet NIC: 10/100M Wi-Fi 802.11 b/g/n/ac Bluetooth® 4.1
+</t>
+  </si>
+  <si>
+    <t>Operating System: Free DOS</t>
+  </si>
+  <si>
+    <t>IT-CSV-39</t>
+  </si>
+  <si>
+    <t>IT-CSV-40</t>
+  </si>
+  <si>
+    <t> 16GB DDR4, 3200MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">512GB M.2 PCIe NVMe Solid State Drive  1TB Hard Drive
+</t>
+  </si>
+  <si>
+    <t>Windows 10 Professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processor Generation: 11th generation Processor Details: Intel® Core™ i7-1165G7 (up to 4.7 GHz with Intel® Turbo Boost Technology, 12 MB L3 cache, 4 cores)
+</t>
+  </si>
+  <si>
+    <t>RAM: 8 GB DDR4-2666 SDRAM (4 GB x 2)</t>
+  </si>
+  <si>
+    <t>Hard drive: 512 GB  PCIe® NVMe™ Value M.2 SSD</t>
+  </si>
+  <si>
+    <t>Display: 15.6" FHD IPS eDP anti-glare slim, 250 nits, 45% NTSC Display Resolution: 1920 x 1080 Display Refresh Rate: 60 Hz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video graphics: NVIDIA GeForce MX450  Video graphics Memory: 2 GB DDR5 dedicated
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel® Dual Band Wireless-AC 9560 802.11a/b/g/n/ac (2x2) Wi-Fi® Bluetooth® 5
+</t>
+  </si>
+  <si>
+    <t>Operating System: Windows 11 Pro</t>
+  </si>
+  <si>
+    <t>Networking:  802.11AC (2 x 2) &amp; Bluetooth® 5.0</t>
+  </si>
+  <si>
+    <t> Ubuntu</t>
+  </si>
+  <si>
+    <t>IT-CSV-41</t>
+  </si>
+  <si>
+    <t>Supports 4G / 3G / 2G</t>
+  </si>
+  <si>
+    <t>Dot Drop, HD + display, 6.53 '' 720x1600 HD +</t>
   </si>
   <si>
     <r>
@@ -81,20 +789,158 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FF282828"/>
+        <rFont val="Roboto"/>
       </rPr>
-      <t>: Android 11, MIUI 12.5</t>
+      <t>: Android 10</t>
     </r>
+  </si>
+  <si>
+    <t>164.9mm × 77.07mm × 9.0mmWeight: 196 g  SIM: Dual SIM (Nano-SIM, dual stand-by)</t>
+  </si>
+  <si>
+    <t>2 GB + 32 GB</t>
+  </si>
+  <si>
+    <t>13-megapixel rear camera Video: 1080P, 30FPS, 60FPS/720p, 30fps</t>
+  </si>
+  <si>
+    <t>5-megapixel selfie camera 1.12μm large pixel size</t>
+  </si>
+  <si>
+    <t>2 + 1 card slot design
+Supports two SIM cards from two different companies; The two cards can connect to the 4G network at the same time
+Supports two nano-SIM cards and micro-SD expansion, and either card can be set as the primary card.
+Supports 4G / 3G / 2G</t>
+  </si>
+  <si>
+    <t>5,000 mAh (typical value) Supports charging capacity of 10 watts</t>
+  </si>
+  <si>
+    <t>IT-CSV-42</t>
+  </si>
+  <si>
+    <t>AMOLED, 450 nits (typ), 1100 nits (peak) 6.43 inches, 99.8 cm2 (~83.5% screen-to-body ratio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">microSDXC (dedicated slot)  128GB 6GB RAM UFS 2.2 </t>
+  </si>
+  <si>
+    <t>Type: Li-Po 5000 mAh, non-removable /Charging: Fast Charging 33W</t>
+  </si>
+  <si>
+    <t>IT-CSV-43</t>
+  </si>
+  <si>
+    <t>LCD, 90Hz 6.5 inches, 102.0 cm2 (~83.4% screen-to-body ratio)</t>
+  </si>
+  <si>
+    <t>microSDXC (dedicated slot) 128GB 6GB RAM  eMMC 5.1</t>
+  </si>
+  <si>
+    <t>Li-Po 5000 mAh, non-removable  Charging: Fast charging 18W</t>
+  </si>
+  <si>
+    <t>165.4 x 76.4 x 8.8 mm/ 183 g</t>
+  </si>
+  <si>
+    <t>IPS LCD /6.6 inches, 105.2 cm2 (~83.2% screen-to-Body ratio)</t>
+  </si>
+  <si>
+    <t>Android 10 (Go edition) /Mediatek MT6761D Helio A20 (12 nm)</t>
+  </si>
+  <si>
+    <t>microSDXC (dedicated slot) /32GB 2GB RAM /eMMC 5.1</t>
+  </si>
+  <si>
+    <r>
+      <t>Single</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF282828"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>: 8 MP</t>
+    </r>
+  </si>
+  <si>
+    <t>IT-CSV-44</t>
+  </si>
+  <si>
+    <t>IT-CSV-45</t>
+  </si>
+  <si>
+    <t>Super AMOLED Plus, 90Hz</t>
+  </si>
+  <si>
+    <t>Android 11, One UI 3.0 /Qualcomm SM7125 Snapdragon 720G (8 nm)</t>
+  </si>
+  <si>
+    <t>165 x 77.4 x 8.4 mm /203 g</t>
+  </si>
+  <si>
+    <t>microSDXC (dedicated slot) 128GB 8GB RAM/UFS 2.1</t>
+  </si>
+  <si>
+    <t>64 MP, f/1.8, 26mm (wide), 1/1.72", 0.8µm, PDAF, OIS</t>
+  </si>
+  <si>
+    <t>32 MP, f/2.2, 26mm (wide), 1/2.8", 0.8µm</t>
+  </si>
+  <si>
+    <t>Li-Ion 5000 mAh, non-removable</t>
+  </si>
+  <si>
+    <t>IT-CSV-46</t>
+  </si>
+  <si>
+    <t> IPS LCD, 120Hz, HDR10, 450 nits (typ) / 6.67 inches, 107.4 cm2 (~84.6% screen-to-body ratio)</t>
+  </si>
+  <si>
+    <t>Android 11, MIUI 12 for POCO/Qualcomm Snapdragon 860 (7 nm)</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF282828"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t>165.3 x 76.8 x 9.4 mm (6.51 x 3.02 x 0.37 in)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF282828"/>
+        <rFont val="Roboto"/>
+      </rPr>
+      <t xml:space="preserve"> / 215 g (7.58 oz)</t>
+    </r>
+  </si>
+  <si>
+    <t>microSDXC (uses shared SIM slot)/256GB 8GB RAM</t>
+  </si>
+  <si>
+    <t>48 MP, f/1.8, (wide), 1/2.0", 0.8µm, PDAF</t>
+  </si>
+  <si>
+    <t>20 MP, f/2.2, (wide), 1/3.4", 0.8µm</t>
+  </si>
+  <si>
+    <t>Li-Po 5160 mAh, non-removable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +951,47 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF282828"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF4A4E5A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF282828"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF282828"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF282828"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,10 +1018,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,66 +1326,4251 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C385"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="77.85546875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B12" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>55</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>55</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>55</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>55</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>64</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>65</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>65</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>73</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>73</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>73</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>73</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>73</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>73</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>73</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>73</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>74</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>74</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>74</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>74</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>74</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>74</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>74</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>83</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>83</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>83</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>83</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>83</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>83</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>83</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>83</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>90</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>90</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>90</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>90</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>90</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>90</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>90</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>90</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>90</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>91</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>91</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>91</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>91</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>91</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>91</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>91</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>91</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>91</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>101</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>101</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>101</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>101</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>101</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>101</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>101</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>101</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>101</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>101</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>102</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>102</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>102</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>102</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>102</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>102</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>102</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>102</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>102</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>103</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>103</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>103</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>103</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>103</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>103</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>103</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>103</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>103</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>104</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>104</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>104</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>104</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>104</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>104</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>104</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>104</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>104</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>108</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>108</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>108</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>108</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>108</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>108</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>108</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>108</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>108</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>109</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>109</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>109</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>109</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>109</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>109</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>109</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>109</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>124</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>124</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>124</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>124</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>124</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>124</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>124</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>124</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>135</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>135</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>135</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>135</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>135</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>135</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>135</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>135</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>144</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>144</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>144</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>144</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>144</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>144</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>144</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>144</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>145</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>145</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>145</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>145</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>145</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>145</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>145</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>145</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>154</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>154</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>154</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>154</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>154</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>154</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>154</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>154</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>155</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>155</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>155</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>155</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>155</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>155</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>155</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>155</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="21" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>156</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>156</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>156</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>156</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>156</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>156</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>156</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>156</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>165</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>165</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>165</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>165</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>165</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>165</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>165</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>165</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>166</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>166</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>166</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>166</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>166</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>166</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>166</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>166</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>167</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>167</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>167</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>167</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>167</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>167</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>167</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>170</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>170</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>170</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>170</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>170</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>170</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>170</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>170</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>181</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>181</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>181</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>181</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>181</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>181</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>182</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>182</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>182</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>182</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>182</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>182</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>182</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>183</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>183</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>183</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>183</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>183</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>183</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>183</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>184</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>184</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>184</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>184</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>184</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>184</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>184</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>208</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>208</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>208</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>208</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>208</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>208</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>208</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>214</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C304" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>214</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C305" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>214</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C306" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>214</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C307" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>214</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C308" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>214</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C309" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>214</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C310" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>221</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>221</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>221</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>221</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>221</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>221</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>221</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>229</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>229</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>229</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>229</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>229</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>229</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C323" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>229</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C324" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>230</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>230</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>230</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>230</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>230</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>230</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>230</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C331" s="10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>243</v>
+      </c>
+      <c r="B332" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>243</v>
+      </c>
+      <c r="B333" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>243</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C334" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>243</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>243</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>243</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>243</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="57" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>243</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C339" s="14" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>243</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>253</v>
+      </c>
+      <c r="B341" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C341" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>253</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C342" s="8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>253</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C343" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>253</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C344" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>253</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C345" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>253</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>253</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C347" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>253</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C348" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>253</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>257</v>
+      </c>
+      <c r="B350" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C350" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>257</v>
+      </c>
+      <c r="B351" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C351" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>257</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>257</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C353" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>257</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C354" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>257</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C355" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>257</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C356" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>257</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C357" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>257</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>266</v>
+      </c>
+      <c r="B359" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C359" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>266</v>
+      </c>
+      <c r="B360" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C360" s="8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>266</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C361" s="11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>266</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C362" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>266</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C363" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>266</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>266</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C365" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>266</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C366" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>266</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C367" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>267</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C368" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>267</v>
+      </c>
+      <c r="B369" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C369" s="8" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>267</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C370" s="8" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>267</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C371" s="11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>267</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C372" s="11" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>267</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C373" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>267</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C374" s="8" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>267</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C375" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>267</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>275</v>
+      </c>
+      <c r="B377" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C377" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>275</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C378" s="8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>275</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C379" s="8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>275</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C380" s="13" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>275</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C381" s="11" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>275</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C382" s="8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>275</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C383" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>275</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C384" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>275</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C385" s="8" t="s">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
